--- a/Output/Matched_Variables.xlsx
+++ b/Output/Matched_Variables.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,20 +468,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>YEAR/MONTH. YEAR/MONTH</t>
+          <t>resp_age. RespondentAge</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YEAR/MONTH</t>
+          <t>resp_age</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> YEAR/MONTH</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t xml:space="preserve"> RespondentAge</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>resp_age</t>
+        </is>
+      </c>
       <c r="E2" t="b">
         <v>0</v>
       </c>
@@ -518,20 +522,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EMP01_. What is your current employment status?</t>
+          <t>GENDER_NONBINARY. Are you...?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EMP01_</t>
+          <t>GENDER_NONBINARY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> What is your current employment status?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t xml:space="preserve"> Are you?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GENDER_NonBinary</t>
+        </is>
+      </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
@@ -541,22 +549,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Comp. Do you currently work at any of the following types of companies?</t>
+          <t>App_Types. Which of the following apps do you use at least once a week?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Comp</t>
+          <t>App_Types</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Do you currently work at any of the following types of companies?</t>
+          <t xml:space="preserve"> Which of the following apps do you use at least once a week?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Comp</t>
+          <t>App_Types</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -568,22 +576,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Job_function. Which of the following best describes your current job function?</t>
+          <t>Reason. What is your primary reason for using health and fitness apps?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Job_function</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which of the following best describes your current job function?</t>
+          <t xml:space="preserve"> What is your primary reason for using health and fitness apps?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Job_function</t>
+          <t>Reason</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -595,22 +603,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Company_type. Which of the following best describes the type of company you work for?</t>
+          <t>Primary_app. Which of the following is the health and fitness app you use most often?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Company_type</t>
+          <t>Primary_app</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which of the following best describes the type of company you work for?</t>
+          <t xml:space="preserve"> Which of the following is the health and fitness app you use most often?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Company_type</t>
+          <t>Primary_app</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -622,22 +630,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Work. Which of the following best describes your day-to-day work?</t>
+          <t>Secondary_app. You've told us about your primary app. Which of the following OTHER apps or devices do you also use at least once a week to manage or track your health and fitness?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Secondary_app</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which of the following best describes your day-to-day work?</t>
+          <t xml:space="preserve"> You've told us about your primary app Which of the following OTHER apps or devices do you also use at least once a week to manage or track your health and fitness?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>Secondary_app</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -649,22 +657,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Industry. Which of the following best describes your industry?</t>
+          <t>Paid_or_free. [AllTrails] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which of the following best describes your industry?</t>
+          <t xml:space="preserve"> [AllTrails] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Paid_or_free[{_1}]._scale</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -676,22 +684,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Job_focus. In your current role, what is your primary area of focus?</t>
+          <t>Paid_or_free. [Apple Fitness / Fitness+] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Job_focus</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> In your current role, what is your primary area of focus?</t>
+          <t xml:space="preserve"> [Apple Fitness / Fitness+] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Job_focus</t>
+          <t>Paid_or_free[{_2}]._scale</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -703,22 +711,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Job_experience. How many years of experience do you have in marketing/advertising?</t>
+          <t>Paid_or_free. [Apple Health] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Job_experience</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How many years of experience do you have in marketing/advertising?</t>
+          <t xml:space="preserve"> [Apple Health] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Job_experience</t>
+          <t>Paid_or_free[{_3}]._scale</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -730,22 +738,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Decision. How involved are you in the decision-making process when choosing how to allocate your advertising budget?</t>
+          <t>Paid_or_free. [Calm] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How involved are you in the decision-making process when choosing how to allocate your advertising budget?</t>
+          <t xml:space="preserve"> [Calm] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Paid_or_free[{_4}]._scale</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -757,22 +765,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform_usage. Which platforms does your company use to run ads?</t>
+          <t>Paid_or_free. [Clue] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Platform_usage</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which platforms does your company use to run ads?</t>
+          <t xml:space="preserve"> [Clue] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Platform_usage</t>
+          <t>Paid_or_free[{_5}]._scale</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -784,22 +792,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spend. [Google Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Fitbit / Fitbit Premium] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Fitbit / Fitbit Premium] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Spend[{_1}]._scale</t>
+          <t>Paid_or_free[{_6}]._scale</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -811,22 +819,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Spend. [Meta Ads (Facebook or Instagram)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Flo] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Meta Ads (Facebook or Instagram)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Flo] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Spend[{_2}]._scale</t>
+          <t>Paid_or_free[{_7}]._scale</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -838,22 +846,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spend. [Microsoft Ads (Bing)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Garmin Connect] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Microsoft Ads (Bing)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Garmin Connect] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Spend[{_3}]._scale</t>
+          <t>Paid_or_free[{_8}]._scale</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -865,22 +873,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spend. [Amazon Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Google Fit] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Amazon Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Google Fit] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Spend[{_4}]._scale</t>
+          <t>Paid_or_free[{_9}]._scale</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -892,22 +900,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spend. [LinkedIn Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Headspace] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [LinkedIn Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Headspace] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Spend[{_5}]._scale</t>
+          <t>Paid_or_free[{_10}]._scale</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -919,22 +927,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spend. [TikTok Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Lose it!] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [TikTok Ads] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Lose it!] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Spend[{_6}]._scale</t>
+          <t>Paid_or_free[{_11}]._scale</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -946,22 +954,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spend. [Google Search Ads 360 (SA360)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Map My (Fitness, Ride, Run, Walk)] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Search Ads 360 (SA360)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Map My (Fitness, Ride, Run, Walk)] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Spend[{_7}]._scale</t>
+          <t>Paid_or_free[{_12}]._scale</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -973,22 +981,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spend. [Google Display &amp;amp; Video 360 (DV360)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [MyFitnessPal] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Display &amp;amp; Video 360 (DV360)] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [MyFitnessPal] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Spend[{_8}]._scale</t>
+          <t>Paid_or_free[{_13}]._scale</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1000,22 +1008,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spend. [The Trade Desk] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t>Paid_or_free. [Nike (Run Club,Training Club)] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spend</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [The Trade Desk] - Which of the following best describes your annual online advertising budget on each of these platforms?</t>
+          <t xml:space="preserve"> [Nike (Run Club,Training Club)] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Spend[{_9}]._scale</t>
+          <t>Paid_or_free[{_14}]._scale</t>
         </is>
       </c>
       <c r="E22" t="b">
@@ -1027,22 +1035,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fam. How familiar are you with a Google Ads tool that allows you to test campaign variations (e.g., split testing or A/B testing)?</t>
+          <t>Paid_or_free. [Noom] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fam</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> How familiar are you with a Google Ads tool that allows you to test campaign variations (eg, split testing or A/B testing)?</t>
+          <t xml:space="preserve"> [Noom] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fam</t>
+          <t>Paid_or_free[{_15}]._scale</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1054,22 +1062,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Locate. Are you able to locate this tool that allows you to test campaign variations in the Google Ads navigation menu?</t>
+          <t>Paid_or_free. [Oura App] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Locate</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Are you able to locate this tool that allows you to test campaign variations in the Google Ads navigation menu?</t>
+          <t xml:space="preserve"> [Oura App] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Locate</t>
+          <t>Paid_or_free[{_16}]._scale</t>
         </is>
       </c>
       <c r="E24" t="b">
@@ -1081,22 +1089,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aware. Which of the following types of tests/measurements are you familiar with, if any?</t>
+          <t>Paid_or_free. [Peloton App] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aware</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which of the following types of tests/measurements are you familiar with, if any?</t>
+          <t xml:space="preserve"> [Peloton App] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AWARE</t>
+          <t>Paid_or_free[{_17}]._scale</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -1108,22 +1116,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Inc_tests. Thinking of all the platforms you use, which of the following types of tests/measurements do you use, if any?</t>
+          <t>Paid_or_free. [Period Tracker] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inc_tests</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Thinking of all the platforms you use, which of the following types of tests/measurements do you use, if any?</t>
+          <t xml:space="preserve"> [Period Tracker] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Inc_tests</t>
+          <t>Paid_or_free[{_18}]._scale</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1135,22 +1143,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Inc_definition. Which of the following do you consider to be a type of incrementality test/measurement?</t>
+          <t>Paid_or_free. [Planet Fitness] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Inc_definition</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which of the following do you consider to be a type of incrementality test/measurement?</t>
+          <t xml:space="preserve"> [Planet Fitness] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Inc_definition</t>
+          <t>Paid_or_free[{_19}]._scale</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -1162,53 +1170,49 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CL_defined. You mentioned you do conversion lift tests/measurements. Which of the following best describes the methodology of the conversion lift tests/measurements you run?</t>
+          <t>Paid_or_free. [Runna] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CL_defined</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> You mentioned you do conversion lift tests/measurements Which of the following best describes the methodology of the conversion lift tests/measurements you run?</t>
+          <t xml:space="preserve"> [Runna] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CL_defined</t>
+          <t>Paid_or_free[{_20}]._scale</t>
         </is>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Inc_tests=2</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tests_marker. Tests_marker</t>
+          <t>Paid_or_free. [Samsung Health] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tests_marker</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Tests_marker</t>
+          <t xml:space="preserve"> [Samsung Health] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tests_marker</t>
+          <t>Paid_or_free[{_21}]._scale</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -1220,22 +1224,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Inc_tools_used. Which platforms do you use to run tests/measurements?</t>
+          <t>Paid_or_free. [Sleep Watch] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Inc_tools_used</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which platforms do you use to run tests/measurements?</t>
+          <t xml:space="preserve"> [Sleep Watch] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Inc_tools_used</t>
+          <t>Paid_or_free[{_22}]._scale</t>
         </is>
       </c>
       <c r="E30" t="b">
@@ -1247,22 +1251,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Inc_tool_interact. Which of the following best describes how you personally use these incrementality tools?</t>
+          <t>Paid_or_free. [Strava] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Inc_tool_interact</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Which of the following best describes how you personally use these incrementality tools?</t>
+          <t xml:space="preserve"> [Strava] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Inc_tool_interact</t>
+          <t>Paid_or_free[{_23}]._scale</t>
         </is>
       </c>
       <c r="E31" t="b">
@@ -1274,22 +1278,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tool_freq. [Google Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Paid_or_free. [WHOOP] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [WHOOP] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tool_freq[{_1}]._scale</t>
+          <t>Paid_or_free[{_24}]._scale</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -1301,22 +1305,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tool_freq. [Meta Ads (Facebook or Instagram)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Paid_or_free. [WW (Weight Watchers)] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Meta Ads (Facebook or Instagram)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [WW (Weight Watchers)] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tool_freq[{_2}]._scale</t>
+          <t>Paid_or_free[{_25}]._scale</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -1328,22 +1332,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tool_freq. [Microsoft Ads (Bing)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Paid_or_free. [Yuka] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Microsoft Ads (Bing)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Yuka] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tool_freq[{_3}]._scale</t>
+          <t>Paid_or_free[{_26}]._scale</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -1355,22 +1359,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tool_freq. [Amazon Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Paid_or_free. [Zepp (Amazfit)] - For each of the following apps, select the option that best describes how you use it.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Paid_or_free</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Amazon Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Zepp (Amazfit)] - For each of the following apps, select the option that best describes how you use it</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tool_freq[{_4}]._scale</t>
+          <t>Paid_or_free[{_27}]._scale</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -1382,103 +1386,115 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tool_freq. [LinkedIn Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Apps_used_marker. Apps_used_marker</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Apps_used_marker</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [LinkedIn Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> Apps_used_marker</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tool_freq[{_5}]._scale</t>
+          <t>Apps_used_marker</t>
         </is>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Apps_used_marker</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tool_freq. [TikTok Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Secondary_marker. Secondary_marker</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Secondary_marker</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [TikTok Ads] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> Secondary_marker</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tool_freq[{_6}]._scale</t>
+          <t>Secondary_marker</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Secondary_marker</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tool_freq. [Google Search Ads 360 (SA360)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Single_vs_ecosystem_marker. Single_vs_ecosystem_marker</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Single_vs_ecosystem_marker</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Search Ads 360 (SA360)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> Single_vs_ecosystem_marker</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tool_freq[{_7}]._scale</t>
+          <t>Single_vs_ecosystem_marker</t>
         </is>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Single_vs_ecosystem_marker</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tool_freq. [Google Display &amp;amp; Video 360 (DV360)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Overall_sat. [Apple Health] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Overall_sat</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Display &amp;amp; Video 360 (DV360)] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Apple Health] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tool_freq[{_8}]._scale</t>
+          <t>Overall_sat[{_1}]._scale</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -1490,22 +1506,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tool_freq. [The Trade Desk] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Overall_sat. [Fitbit / Fitbit Premium] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Overall_sat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [The Trade Desk] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Fitbit / Fitbit Premium] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tool_freq[{_9}]._scale</t>
+          <t>Overall_sat[{_2}]._scale</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -1517,22 +1533,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tool_freq. [LiftLab] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Overall_sat. [Garmin Connect] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Overall_sat</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [LiftLab] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Garmin Connect] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tool_freq[{_11}]._scale</t>
+          <t>Overall_sat[{_3}]._scale</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -1544,22 +1560,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tool_freq. [Measured] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Overall_sat. [Oura App] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Overall_sat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Measured] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Oura App] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tool_freq[{_12}]._scale</t>
+          <t>Overall_sat[{_4}]._scale</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -1571,22 +1587,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tool_freq. [Haus] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Overall_sat. [Samsung Health] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Overall_sat</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Haus] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Samsung Health] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tool_freq[{_13}]._scale</t>
+          <t>Overall_sat[{_5}]._scale</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -1598,22 +1614,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tool_freq. [AppsFlyer] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Overall_sat. [Strava] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Overall_sat</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AppsFlyer] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Strava] - Overall, how satisfied are you with how this app helps you achieve your health goals?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tool_freq[{_14}]._scale</t>
+          <t>Overall_sat[{_6}]._scale</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -1625,76 +1641,84 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tool_freq. [Nielsen] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>App_consideration. Have you considered using other apps or devices in addition to your primary health and fitness app?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>App_consideration</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Nielsen] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> Have you considered using other apps or devices in addition to your primary health and fitness app?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tool_freq[{_15}]._scale</t>
+          <t>App_consideration</t>
         </is>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Single_vs_ecosystem_marker=Single app users</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tool_freq. [Platform_usage_Other] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>Ecosystem_reasons. Why do you use secondary tools in addition to your primary health and fitness app?</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>Ecosystem_reasons</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Platform_usage_Other] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> Why do you use secondary tools in addition to your primary health and fitness app?</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tool_freq[{_98}]._scale</t>
+          <t>Ecosystem_reasons</t>
         </is>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Single_vs_ecosystem_marker=Micro-Ecosystem users</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tool_freq. [Inc_tools_used_Other] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t>KANO. [Review a quick summary of my daily health data at a glance] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tool_freq</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Inc_tools_used_Other] - How frequently are you personally logging into the reporting or measurement tools you use for your ads?</t>
+          <t xml:space="preserve"> [Review a quick summary of my daily health data at a glance] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tool_freq[{_97}]._scale</t>
+          <t>KANO[{_1}]._scale</t>
         </is>
       </c>
       <c r="E47" t="b">
@@ -1706,22 +1730,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Decision_marker. Decision_marker</t>
+          <t>KANO. [See my progress and trends over time] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Decision_marker</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Decision_marker</t>
+          <t xml:space="preserve"> [See my progress and trends over time] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Decision_marker</t>
+          <t>KANO[{_2}]._scale</t>
         </is>
       </c>
       <c r="E48" t="b">
@@ -1733,22 +1757,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>User_marker. User_marker</t>
+          <t>KANO. [See all my health and wellness data from different apps in one place] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>User_marker</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> User_marker</t>
+          <t xml:space="preserve"> [See all my health and wellness data from different apps in one place] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>User_marker</t>
+          <t>KANO[{_3}]._scale</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -1760,22 +1784,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [A/B experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [A/B experiments]}.</t>
+          <t>KANO. [Follow a structured workout or training plan] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [A/B experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [A/B experiments]}</t>
+          <t xml:space="preserve"> [Follow a structured workout or training plan] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_1}]._scale</t>
+          <t>KANO[{_4}]._scale</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -1787,22 +1811,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [A/B tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [A/B tests]}.</t>
+          <t>KANO. [Accurately track a specific workout (e.g., a run, gym session)] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [A/B tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [A/B tests]}</t>
+          <t xml:space="preserve"> [Accurately track a specific workout (eg, a run, gym session)] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_2}]._scale</t>
+          <t>KANO[{_5}]._scale</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -1814,22 +1838,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Comparison tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Comparison tests]}.</t>
+          <t>KANO. [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Comparison tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Comparison tests]}</t>
+          <t xml:space="preserve"> [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_3}]._scale</t>
+          <t>KANO[{_6}]._scale</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -1841,22 +1865,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Experiments]}.</t>
+          <t>KANO. [Understand my sleep quality, patterns, and duration] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Experiments]}</t>
+          <t xml:space="preserve"> [Understand my sleep quality, patterns, and duration] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_4}]._scale</t>
+          <t>KANO[{_7}]._scale</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -1868,22 +1892,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Multi-variant experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Multi-variant experiments]}.</t>
+          <t>KANO. [Know if my body is physically recovered and ready for a workout] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Multi-variant experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Multi-variant experiments]}</t>
+          <t xml:space="preserve"> [Know if my body is physically recovered and ready for a workout] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_5}]._scale</t>
+          <t>KANO[{_8}]._scale</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -1895,22 +1919,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Multi-variant tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Multi-variant tests]}.</t>
+          <t>KANO. [Build and maintain healthy sleep habits] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Multi-variant tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Multi-variant tests]}</t>
+          <t xml:space="preserve"> [Build and maintain healthy sleep habits] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_6}]._scale</t>
+          <t>KANO[{_9}]._scale</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -1922,22 +1946,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Lift experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Lift experiments]}.</t>
+          <t>KANO. [Set health and fitness goals that are right for me] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Lift experiments] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Lift experiments]}</t>
+          <t xml:space="preserve"> [Set health and fitness goals that are right for me] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_100}]._scale</t>
+          <t>KANO[{_10}]._scale</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -1949,22 +1973,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Lift tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Lift tests]}.</t>
+          <t>KANO. [Get recognized for my achievements (e.g., badges, awards)] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Lift tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Lift tests]}</t>
+          <t xml:space="preserve"> [Get recognized for my achievements (eg, badges, awards)] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_101}]._scale</t>
+          <t>KANO[{_11}]._scale</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -1976,22 +2000,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Lift studies] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Lift studies]}.</t>
+          <t>KANO. [Track my nutrition and activity to reach a weight goal] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Lift studies] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Lift studies]}</t>
+          <t xml:space="preserve"> [Track my nutrition and activity to reach a weight goal] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_102}]._scale</t>
+          <t>KANO[{_12}]._scale</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -2003,22 +2027,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Impact tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Impact tests]}.</t>
+          <t>KANO. [Accurately track my menstrual cycle and understand its patterns] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Impact tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Impact tests]}</t>
+          <t xml:space="preserve"> [Accurately track my menstrual cycle and understand its patterns] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_103}]._scale</t>
+          <t>KANO[{_13}]._scale</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -2030,22 +2054,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Q8. [AB testing tab then Lift studies tab] - [Causal tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Causal tests]}.</t>
+          <t>KANO. [Easily log my mood, thoughts, or feelings] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Causal tests] - Based on the following name, how interested are you in learning more about a {[AB testing tab then Lift studies tab] - [Causal tests]}</t>
+          <t xml:space="preserve"> [Easily log my mood, thoughts, or feelings] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q8[{_104}]._scale</t>
+          <t>KANO[{_14}]._scale</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -2057,22 +2081,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [A/B experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [A/B experiments]}.</t>
+          <t>KANO. [Track and manage my medication schedule] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [A/B experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [A/B experiments]}</t>
+          <t xml:space="preserve"> [Track and manage my medication schedule] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_1}]._scale</t>
+          <t>KANO[{_15}]._scale</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -2084,22 +2108,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [A/B tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [A/B tests]}.</t>
+          <t>KANO. [Monitor key biomarkers like blood pressure or glucose] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [A/B tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [A/B tests]}</t>
+          <t xml:space="preserve"> [Monitor key biomarkers like blood pressure or glucose] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_2}]._scale</t>
+          <t>KANO[{_16}]._scale</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -2111,22 +2135,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Comparison tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Comparison tests]}.</t>
+          <t>KANO. [Follow guidance to build my long-term mental wellbeing] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Comparison tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Comparison tests]}</t>
+          <t xml:space="preserve"> [Follow guidance to build my long-term mental wellbeing] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_3}]._scale</t>
+          <t>KANO[{_17}]._scale</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -2138,22 +2162,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Experiments]}.</t>
+          <t>KANO. [Get personalized recommendations on what to do next based on my data] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Experiments]}</t>
+          <t xml:space="preserve"> [Get personalized recommendations on what to do next based on my data] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_4}]._scale</t>
+          <t>KANO[{_18}]._scale</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -2165,22 +2189,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Multi-variant experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Multi-variant experiments]}.</t>
+          <t>KANO. [Get motivation and accountability from friends and family] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Multi-variant experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Multi-variant experiments]}</t>
+          <t xml:space="preserve"> [Get motivation and accountability from friends and family] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_5}]._scale</t>
+          <t>KANO[{_19}]._scale</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -2192,22 +2216,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Multi-variant tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Multi-variant tests]}.</t>
+          <t>KANO. [Share and celebrate my health achievements with others] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Multi-variant tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Multi-variant tests]}</t>
+          <t xml:space="preserve"> [Share and celebrate my health achievements with others] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_6}]._scale</t>
+          <t>KANO[{_20}]._scale</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -2219,22 +2243,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Lift experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Lift experiments]}.</t>
+          <t>KANO. [Control who I'm connected with and what data I share] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Lift experiments] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Lift experiments]}</t>
+          <t xml:space="preserve"> [Control who I'm connected with and what data I share] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_100}]._scale</t>
+          <t>KANO[{_21}]._scale</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -2246,22 +2270,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Lift tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Lift tests]}.</t>
+          <t>KANO. [Get answers to my health questions] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>KANO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Lift tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Lift tests]}</t>
+          <t xml:space="preserve"> [Get answers to my health questions] - Which statement best describes how you feel about each of these goals?</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_101}]._scale</t>
+          <t>KANO[{_22}]._scale</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -2273,22 +2297,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Lift studies] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Lift studies]}.</t>
+          <t>QAware. [Review a quick summary of my daily health data at a glance] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Lift studies] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Lift studies]}</t>
+          <t xml:space="preserve"> [Review a quick summary of my daily health data at a glance] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_102}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_1}].QAware</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -2300,22 +2324,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Impact tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Impact tests]}.</t>
+          <t>QAware. [See my progress and trends over time] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Impact tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Impact tests]}</t>
+          <t xml:space="preserve"> [See my progress and trends over time] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_103}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_2}].QAware</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -2327,22 +2351,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Q8. [Lift studies tab then AB testing tab] - [Causal tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Causal tests]}.</t>
+          <t>QAware. [See all my health and wellness data from different apps in one place] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Causal tests] - Based on the following name, how interested are you in learning more about a {[Lift studies tab then AB testing tab] - [Causal tests]}</t>
+          <t xml:space="preserve"> [See all my health and wellness data from different apps in one place] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q8[{_104}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_3}].QAware</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -2354,20 +2378,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Q8_Combine. [A/B experiments] - Based on the following name, how interested are you in learning more about a [A/B experiments]</t>
+          <t>QAware. [Follow a structured workout or training plan] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [A/B experiments] - Based on the following name, how interested are you in learning more about a [A/B experiments]</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t xml:space="preserve"> [Follow a structured workout or training plan] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_4}].QAware</t>
+        </is>
+      </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
@@ -2377,20 +2405,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Q8_Combine. [A/B tests] - Based on the following name, how interested are you in learning more about a [A/B tests]</t>
+          <t>QAware. [Accurately track a specific workout (e.g., a run, gym session)] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [A/B tests] - Based on the following name, how interested are you in learning more about a [A/B tests]</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t xml:space="preserve"> [Accurately track a specific workout (eg, a run, gym session)] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_5}].QAware</t>
+        </is>
+      </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
@@ -2400,20 +2432,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Comparison tests] - Based on the following name, how interested are you in learning more about a [Comparison tests]</t>
+          <t>QAware. [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Comparison tests] - Based on the following name, how interested are you in learning more about a [Comparison tests]</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t xml:space="preserve"> [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_6}].QAware</t>
+        </is>
+      </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
@@ -2423,20 +2459,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Experiments] - Based on the following name, how interested are you in learning more about a [Experiments]</t>
+          <t>QAware. [Understand my sleep quality, patterns, and duration] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiments] - Based on the following name, how interested are you in learning more about a [Experiments]</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t xml:space="preserve"> [Understand my sleep quality, patterns, and duration] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_7}].QAware</t>
+        </is>
+      </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
@@ -2446,20 +2486,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Multi-variant experiments] - Based on the following name, how interested are you in learning more about a [Multi-variant experiments]</t>
+          <t>QAware. [Know if my body is physically recovered and ready for a workout] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Multi-variant experiments] - Based on the following name, how interested are you in learning more about a [Multi-variant experiments]</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t xml:space="preserve"> [Know if my body is physically recovered and ready for a workout] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_8}].QAware</t>
+        </is>
+      </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
@@ -2469,20 +2513,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Multi-variant tests] - Based on the following name, how interested are you in learning more about a [Multi-variant tests]</t>
+          <t>QAware. [Build and maintain healthy sleep habits] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Multi-variant tests] - Based on the following name, how interested are you in learning more about a [Multi-variant tests]</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t xml:space="preserve"> [Build and maintain healthy sleep habits] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_9}].QAware</t>
+        </is>
+      </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
@@ -2492,20 +2540,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Lift experiments] - Based on the following name, how interested are you in learning more about a [Lift experiments]</t>
+          <t>QAware. [Set health and fitness goals that are right for me] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift experiments] - Based on the following name, how interested are you in learning more about a [Lift experiments]</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t xml:space="preserve"> [Set health and fitness goals that are right for me] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_10}].QAware</t>
+        </is>
+      </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
@@ -2515,20 +2567,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Lift tests] - Based on the following name, how interested are you in learning more about a [Lift tests]</t>
+          <t>QAware. [Get recognized for my achievements (e.g., badges, awards)] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift tests] - Based on the following name, how interested are you in learning more about a [Lift tests]</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t xml:space="preserve"> [Get recognized for my achievements (eg, badges, awards)] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_11}].QAware</t>
+        </is>
+      </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
@@ -2538,20 +2594,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Lift studies] - Based on the following name, how interested are you in learning more about a [Lift studies]</t>
+          <t>QAware. [Track my nutrition and activity to reach a weight goal] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies] - Based on the following name, how interested are you in learning more about a [Lift studies]</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t xml:space="preserve"> [Track my nutrition and activity to reach a weight goal] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_12}].QAware</t>
+        </is>
+      </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
@@ -2561,20 +2621,24 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Impact tests] - Based on the following name, how interested are you in learning more about a [Impact tests]</t>
+          <t>QAware. [Accurately track my menstrual cycle and understand its patterns] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Impact tests] - Based on the following name, how interested are you in learning more about a [Impact tests]</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t xml:space="preserve"> [Accurately track my menstrual cycle and understand its patterns] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_13}].QAware</t>
+        </is>
+      </c>
       <c r="E81" t="b">
         <v>0</v>
       </c>
@@ -2584,20 +2648,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Q8_Combine. [Causal tests] - Based on the following name, how interested are you in learning more about a [Causal tests]</t>
+          <t>QAware. [Easily log my mood, thoughts, or feelings] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Q8_Combine</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Causal tests] - Based on the following name, how interested are you in learning more about a [Causal tests]</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t xml:space="preserve"> [Easily log my mood, thoughts, or feelings] - Are you aware of any features on Primary_app that help you with this goal?</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_14}].QAware</t>
+        </is>
+      </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
@@ -2607,22 +2675,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Q9. [AB testing tab then Lift studies tab] - [Helps me understand what I can do on this tab] - We would now like to know more about what you think of when you see each name. {[AB testing tab then Lift studies tab] - [Helps me understand what I can do on this tab]}.</t>
+          <t>QAware. [Track and manage my medication schedule] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Helps me understand what I can do on this tab] - We would now like to know more about what you think of when you see each name {[AB testing tab then Lift studies tab] - [Helps me understand what I can do on this tab]}</t>
+          <t xml:space="preserve"> [Track and manage my medication schedule] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q9[{_1}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_15}].QAware</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -2634,22 +2702,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Q9. [AB testing tab then Lift studies tab] - [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name. {[AB testing tab then Lift studies tab] - [Uses clear, everyday language]}.</t>
+          <t>QAware. [Monitor key biomarkers like blood pressure or glucose] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name {[AB testing tab then Lift studies tab] - [Uses clear, everyday language]}</t>
+          <t xml:space="preserve"> [Monitor key biomarkers like blood pressure or glucose] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q9[{_2}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_16}].QAware</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -2661,22 +2729,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Q9. [AB testing tab then Lift studies tab] - [Leaves a positive impression] - We would now like to know more about what you think of when you see each name. {[AB testing tab then Lift studies tab] - [Leaves a positive impression]}.</t>
+          <t>QAware. [Follow guidance to build my long-term mental wellbeing] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Leaves a positive impression] - We would now like to know more about what you think of when you see each name {[AB testing tab then Lift studies tab] - [Leaves a positive impression]}</t>
+          <t xml:space="preserve"> [Follow guidance to build my long-term mental wellbeing] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q9[{_3}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_17}].QAware</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -2688,22 +2756,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Q9. [AB testing tab then Lift studies tab] - [Conveys innovative technology] - We would now like to know more about what you think of when you see each name. {[AB testing tab then Lift studies tab] - [Conveys innovative technology]}.</t>
+          <t>QAware. [Get personalized recommendations on what to do next based on my data] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Conveys innovative technology] - We would now like to know more about what you think of when you see each name {[AB testing tab then Lift studies tab] - [Conveys innovative technology]}</t>
+          <t xml:space="preserve"> [Get personalized recommendations on what to do next based on my data] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q9[{_4}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_18}].QAware</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -2715,22 +2783,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Q9. [AB testing tab then Lift studies tab] - [Sounds familiar] - We would now like to know more about what you think of when you see each name. {[AB testing tab then Lift studies tab] - [Sounds familiar]}.</t>
+          <t>QAware. [Get motivation and accountability from friends and family] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Sounds familiar] - We would now like to know more about what you think of when you see each name {[AB testing tab then Lift studies tab] - [Sounds familiar]}</t>
+          <t xml:space="preserve"> [Get motivation and accountability from friends and family] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q9[{_5}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_19}].QAware</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -2742,22 +2810,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Q9. [Lift studies tab then AB testing tab] - [Helps me understand what I can do on this tab] - We would now like to know more about what you think of when you see each name. {[Lift studies tab then AB testing tab] - [Helps me understand what I can do on this tab]}.</t>
+          <t>QAware. [Share and celebrate my health achievements with others] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Helps me understand what I can do on this tab] - We would now like to know more about what you think of when you see each name {[Lift studies tab then AB testing tab] - [Helps me understand what I can do on this tab]}</t>
+          <t xml:space="preserve"> [Share and celebrate my health achievements with others] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q9[{_1}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_20}].QAware</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -2769,22 +2837,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Q9. [Lift studies tab then AB testing tab] - [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name. {[Lift studies tab then AB testing tab] - [Uses clear, everyday language]}.</t>
+          <t>QAware. [Control who I'm connected with and what data I share] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name {[Lift studies tab then AB testing tab] - [Uses clear, everyday language]}</t>
+          <t xml:space="preserve"> [Control who I'm connected with and what data I share] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q9[{_2}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_21}].QAware</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -2796,22 +2864,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Q9. [Lift studies tab then AB testing tab] - [Leaves a positive impression] - We would now like to know more about what you think of when you see each name. {[Lift studies tab then AB testing tab] - [Leaves a positive impression]}.</t>
+          <t>QAware. [Get answers to my health questions] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QAware</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Leaves a positive impression] - We would now like to know more about what you think of when you see each name {[Lift studies tab then AB testing tab] - [Leaves a positive impression]}</t>
+          <t xml:space="preserve"> [Get answers to my health questions] - Are you aware of any features on Primary_app that help you with this goal?</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q9[{_3}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_22}].QAware</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -2823,22 +2891,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Q9. [Lift studies tab then AB testing tab] - [Conveys innovative technology] - We would now like to know more about what you think of when you see each name. {[Lift studies tab then AB testing tab] - [Conveys innovative technology]}.</t>
+          <t>QUsage. [Review a quick summary of my daily health data at a glance] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Conveys innovative technology] - We would now like to know more about what you think of when you see each name {[Lift studies tab then AB testing tab] - [Conveys innovative technology]}</t>
+          <t xml:space="preserve"> [Review a quick summary of my daily health data at a glance] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q9[{_4}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_1}].QUsage</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -2850,22 +2918,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Q9. [Lift studies tab then AB testing tab] - [Sounds familiar] - We would now like to know more about what you think of when you see each name. {[Lift studies tab then AB testing tab] - [Sounds familiar]}.</t>
+          <t>QUsage. [See my progress and trends over time] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Sounds familiar] - We would now like to know more about what you think of when you see each name {[Lift studies tab then AB testing tab] - [Sounds familiar]}</t>
+          <t xml:space="preserve"> [See my progress and trends over time] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q9[{_5}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_2}].QUsage</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -2877,20 +2945,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Q9_Combine. [Helps me understand what I can do on this] - We would now like to know more about what you think of when you see each name [Helps me understand what I can do on this]</t>
+          <t>QUsage. [See all my health and wellness data from different apps in one place] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Q9_Combine</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Helps me understand what I can do on this] - We would now like to know more about what you think of when you see each name [Helps me understand what I can do on this]</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t xml:space="preserve"> [See all my health and wellness data from different apps in one place] - How often do you use features to help you with this goal on Primary_app</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_3}].QUsage</t>
+        </is>
+      </c>
       <c r="E93" t="b">
         <v>0</v>
       </c>
@@ -2900,20 +2972,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Q9_Combine. [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name [Uses clear, everyday language]</t>
+          <t>QUsage. [Follow a structured workout or training plan] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Q9_Combine</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name [Uses clear, everyday language]</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t xml:space="preserve"> [Follow a structured workout or training plan] - How often do you use features to help you with this goal on Primary_app</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_4}].QUsage</t>
+        </is>
+      </c>
       <c r="E94" t="b">
         <v>0</v>
       </c>
@@ -2923,20 +2999,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Q9_Combine. [Leaves a positive impression] - We would now like to know more about what you think of when you see each name [Leaves a positive impression]</t>
+          <t>QUsage. [Accurately track a specific workout (e.g., a run, gym session)] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Q9_Combine</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Leaves a positive impression] - We would now like to know more about what you think of when you see each name [Leaves a positive impression]</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t xml:space="preserve"> [Accurately track a specific workout (eg, a run, gym session)] - How often do you use features to help you with this goal on Primary_app</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_5}].QUsage</t>
+        </is>
+      </c>
       <c r="E95" t="b">
         <v>0</v>
       </c>
@@ -2946,20 +3026,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Q9_Combine. [Conveys innovative technology] - We would now like to know more about what you think of when you see each name [Conveys innovative technology]</t>
+          <t>QUsage. [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Q9_Combine</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Conveys innovative technology] - We would now like to know more about what you think of when you see each name [Conveys innovative technology]</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t xml:space="preserve"> [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - How often do you use features to help you with this goal on Primary_app</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_6}].QUsage</t>
+        </is>
+      </c>
       <c r="E96" t="b">
         <v>0</v>
       </c>
@@ -2969,20 +3053,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Q9_Combine. [Sounds familiar] - We would now like to know more about what you think of when you see each name [Sounds familiar]</t>
+          <t>QUsage. [Understand my sleep quality, patterns, and duration] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Q9_Combine</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Sounds familiar] - We would now like to know more about what you think of when you see each name [Sounds familiar]</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t xml:space="preserve"> [Understand my sleep quality, patterns, and duration] - How often do you use features to help you with this goal on Primary_app</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_7}].QUsage</t>
+        </is>
+      </c>
       <c r="E97" t="b">
         <v>0</v>
       </c>
@@ -2992,22 +3080,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [A/B experiments] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [A/B experiments]}.</t>
+          <t>QUsage. [Know if my body is physically recovered and ready for a workout] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [A/B experiments] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [A/B experiments]}</t>
+          <t xml:space="preserve"> [Know if my body is physically recovered and ready for a workout] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_1}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_8}].QUsage</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -3019,22 +3107,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [A/B tests] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [A/B tests]}.</t>
+          <t>QUsage. [Build and maintain healthy sleep habits] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [A/B tests] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [A/B tests]}</t>
+          <t xml:space="preserve"> [Build and maintain healthy sleep habits] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_2}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_9}].QUsage</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -3046,22 +3134,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Comparison tests] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Comparison tests]}.</t>
+          <t>QUsage. [Set health and fitness goals that are right for me] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Comparison tests] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Comparison tests]}</t>
+          <t xml:space="preserve"> [Set health and fitness goals that are right for me] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_3}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_10}].QUsage</t>
         </is>
       </c>
       <c r="E100" t="b">
@@ -3073,22 +3161,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Experiments] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Experiments]}.</t>
+          <t>QUsage. [Get recognized for my achievements (e.g., badges, awards)] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Experiments] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Experiments]}</t>
+          <t xml:space="preserve"> [Get recognized for my achievements (eg, badges, awards)] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_4}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_11}].QUsage</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -3100,22 +3188,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Multi-variant experiments] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Multi-variant experiments]}.</t>
+          <t>QUsage. [Track my nutrition and activity to reach a weight goal] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Multi-variant experiments] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Multi-variant experiments]}</t>
+          <t xml:space="preserve"> [Track my nutrition and activity to reach a weight goal] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_5}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_12}].QUsage</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -3127,22 +3215,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Multi-variant tests] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Multi-variant tests]}.</t>
+          <t>QUsage. [Accurately track my menstrual cycle and understand its patterns] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Multi-variant tests] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Multi-variant tests]}</t>
+          <t xml:space="preserve"> [Accurately track my menstrual cycle and understand its patterns] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_6}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_13}].QUsage</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -3154,22 +3242,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Lift experiments] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Lift experiments]}.</t>
+          <t>QUsage. [Easily log my mood, thoughts, or feelings] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Lift experiments] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Lift experiments]}</t>
+          <t xml:space="preserve"> [Easily log my mood, thoughts, or feelings] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_100}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_14}].QUsage</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -3181,22 +3269,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Lift tests] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Lift tests]}.</t>
+          <t>QUsage. [Track and manage my medication schedule] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Lift tests] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Lift tests]}</t>
+          <t xml:space="preserve"> [Track and manage my medication schedule] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_101}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_15}].QUsage</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -3208,22 +3296,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Lift studies] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Lift studies]}.</t>
+          <t>QUsage. [Monitor key biomarkers like blood pressure or glucose] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Lift studies] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Lift studies]}</t>
+          <t xml:space="preserve"> [Monitor key biomarkers like blood pressure or glucose] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_102}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_16}].QUsage</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -3235,22 +3323,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Impact tests] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Impact tests]}.</t>
+          <t>QUsage. [Follow guidance to build my long-term mental wellbeing] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Impact tests] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Impact tests]}</t>
+          <t xml:space="preserve"> [Follow guidance to build my long-term mental wellbeing] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_103}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_17}].QUsage</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -3262,22 +3350,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Q10. [AB testing tab then Lift studies tab] - [Causal tests] - Based on the description you read, how well does this name work for the tab. {[AB testing tab then Lift studies tab] - [Causal tests]}.</t>
+          <t>QUsage. [Get personalized recommendations on what to do next based on my data] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - [Causal tests] - Based on the description you read, how well does this name work for the tab {[AB testing tab then Lift studies tab] - [Causal tests]}</t>
+          <t xml:space="preserve"> [Get personalized recommendations on what to do next based on my data] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q10[{_104}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_18}].QUsage</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -3289,22 +3377,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [A/B experiments] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [A/B experiments]}.</t>
+          <t>QUsage. [Get motivation and accountability from friends and family] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [A/B experiments] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [A/B experiments]}</t>
+          <t xml:space="preserve"> [Get motivation and accountability from friends and family] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_1}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_19}].QUsage</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -3316,22 +3404,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [A/B tests] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [A/B tests]}.</t>
+          <t>QUsage. [Share and celebrate my health achievements with others] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [A/B tests] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [A/B tests]}</t>
+          <t xml:space="preserve"> [Share and celebrate my health achievements with others] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_2}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_20}].QUsage</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -3343,22 +3431,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Comparison tests] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Comparison tests]}.</t>
+          <t>QUsage. [Control who I'm connected with and what data I share] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Comparison tests] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Comparison tests]}</t>
+          <t xml:space="preserve"> [Control who I'm connected with and what data I share] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_3}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_21}].QUsage</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -3370,22 +3458,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Experiments] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Experiments]}.</t>
+          <t>QUsage. [Get answers to my health questions] - How often do you use features to help you with this goal on Primary_app.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>QUsage</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Experiments] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Experiments]}</t>
+          <t xml:space="preserve"> [Get answers to my health questions] - How often do you use features to help you with this goal on Primary_app</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_4}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_22}].QUsage</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -3397,568 +3485,704 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Multi-variant experiments] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Multi-variant experiments]}.</t>
+          <t>Qsat. [Review a quick summary of my daily health data at a glance] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Multi-variant experiments] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Multi-variant experiments]}</t>
+          <t xml:space="preserve"> [Review a quick summary of my daily health data at a glance] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_5}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_1}].QSat</t>
         </is>
       </c>
       <c r="E113" t="b">
         <v>0</v>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Multi-variant tests] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Multi-variant tests]}.</t>
+          <t>Qsat. [See my progress and trends over time] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Multi-variant tests] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Multi-variant tests]}</t>
+          <t xml:space="preserve"> [See my progress and trends over time] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_6}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_2}].QSat</t>
         </is>
       </c>
       <c r="E114" t="b">
         <v>0</v>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Lift experiments] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Lift experiments]}.</t>
+          <t>Qsat. [See all my health and wellness data from different apps in one place] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Lift experiments] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Lift experiments]}</t>
+          <t xml:space="preserve"> [See all my health and wellness data from different apps in one place] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_100}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_3}].QSat</t>
         </is>
       </c>
       <c r="E115" t="b">
         <v>0</v>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Lift tests] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Lift tests]}.</t>
+          <t>Qsat. [Follow a structured workout or training plan] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Lift tests] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Lift tests]}</t>
+          <t xml:space="preserve"> [Follow a structured workout or training plan] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_101}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_4}].QSat</t>
         </is>
       </c>
       <c r="E116" t="b">
         <v>0</v>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Lift studies] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Lift studies]}.</t>
+          <t>Qsat. [Accurately track a specific workout (e.g., a run, gym session)] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Lift studies] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Lift studies]}</t>
+          <t xml:space="preserve"> [Accurately track a specific workout (eg, a run, gym session)] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_102}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_5}].QSat</t>
         </is>
       </c>
       <c r="E117" t="b">
         <v>0</v>
       </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Impact tests] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Impact tests]}.</t>
+          <t>Qsat. [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Impact tests] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Impact tests]}</t>
+          <t xml:space="preserve"> [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_103}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_6}].QSat</t>
         </is>
       </c>
       <c r="E118" t="b">
         <v>0</v>
       </c>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Q10. [Lift studies tab then AB testing tab] - [Causal tests] - Based on the description you read, how well does this name work for the tab. {[Lift studies tab then AB testing tab] - [Causal tests]}.</t>
+          <t>Qsat. [Understand my sleep quality, patterns, and duration] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - [Causal tests] - Based on the description you read, how well does this name work for the tab {[Lift studies tab then AB testing tab] - [Causal tests]}</t>
+          <t xml:space="preserve"> [Understand my sleep quality, patterns, and duration] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q10[{_104}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_7}].QSat</t>
         </is>
       </c>
       <c r="E119" t="b">
         <v>0</v>
       </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Q10_Combine. [A/B experiments] - Based on the description you read, how well does this name work for the tab [A/B experiments]</t>
+          <t>Qsat. [Know if my body is physically recovered and ready for a workout] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [A/B experiments] - Based on the description you read, how well does this name work for the tab [A/B experiments]</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t xml:space="preserve"> [Know if my body is physically recovered and ready for a workout] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_8}].QSat</t>
+        </is>
+      </c>
       <c r="E120" t="b">
         <v>0</v>
       </c>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Q10_Combine. [A/B tests] - Based on the description you read, how well does this name work for the tab [A/B tests]</t>
+          <t>Qsat. [Build and maintain healthy sleep habits] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [A/B tests] - Based on the description you read, how well does this name work for the tab [A/B tests]</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t xml:space="preserve"> [Build and maintain healthy sleep habits] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_9}].QSat</t>
+        </is>
+      </c>
       <c r="E121" t="b">
         <v>0</v>
       </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Comparison tests] - Based on the description you read, how well does this name work for the tab [Comparison tests]</t>
+          <t>Qsat. [Set health and fitness goals that are right for me] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Comparison tests] - Based on the description you read, how well does this name work for the tab [Comparison tests]</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t xml:space="preserve"> [Set health and fitness goals that are right for me] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_10}].QSat</t>
+        </is>
+      </c>
       <c r="E122" t="b">
         <v>0</v>
       </c>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Experiments] - Based on the description you read, how well does this name work for the tab [Experiments]</t>
+          <t>Qsat. [Get recognized for my achievements (e.g., badges, awards)] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiments] - Based on the description you read, how well does this name work for the tab [Experiments]</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t xml:space="preserve"> [Get recognized for my achievements (eg, badges, awards)] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_11}].QSat</t>
+        </is>
+      </c>
       <c r="E123" t="b">
         <v>0</v>
       </c>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Multi-variant experiments] - Based on the description you read, how well does this name work for the tab [Multi-variant experiments]</t>
+          <t>Qsat. [Track my nutrition and activity to reach a weight goal] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Multi-variant experiments] - Based on the description you read, how well does this name work for the tab [Multi-variant experiments]</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t xml:space="preserve"> [Track my nutrition and activity to reach a weight goal] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_12}].QSat</t>
+        </is>
+      </c>
       <c r="E124" t="b">
         <v>0</v>
       </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Multi-variant tests] - Based on the description you read, how well does this name work for the tab [Multi-variant tests]</t>
+          <t>Qsat. [Accurately track my menstrual cycle and understand its patterns] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Multi-variant tests] - Based on the description you read, how well does this name work for the tab [Multi-variant tests]</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t xml:space="preserve"> [Accurately track my menstrual cycle and understand its patterns] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_13}].QSat</t>
+        </is>
+      </c>
       <c r="E125" t="b">
         <v>0</v>
       </c>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Lift experiments] - Based on the description you read, how well does this name work for the tab [Lift experiments]</t>
+          <t>Qsat. [Easily log my mood, thoughts, or feelings] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift experiments] - Based on the description you read, how well does this name work for the tab [Lift experiments]</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t xml:space="preserve"> [Easily log my mood, thoughts, or feelings] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_14}].QSat</t>
+        </is>
+      </c>
       <c r="E126" t="b">
         <v>0</v>
       </c>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Lift tests] - Based on the description you read, how well does this name work for the tab [Lift tests]</t>
+          <t>Qsat. [Track and manage my medication schedule] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift tests] - Based on the description you read, how well does this name work for the tab [Lift tests]</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t xml:space="preserve"> [Track and manage my medication schedule] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_15}].QSat</t>
+        </is>
+      </c>
       <c r="E127" t="b">
         <v>0</v>
       </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Lift studies] - Based on the description you read, how well does this name work for the tab [Lift studies]</t>
+          <t>Qsat. [Monitor key biomarkers like blood pressure or glucose] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies] - Based on the description you read, how well does this name work for the tab [Lift studies]</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t xml:space="preserve"> [Monitor key biomarkers like blood pressure or glucose] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_16}].QSat</t>
+        </is>
+      </c>
       <c r="E128" t="b">
         <v>0</v>
       </c>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Impact tests] - Based on the description you read, how well does this name work for the tab [Impact tests]</t>
+          <t>Qsat. [Follow guidance to build my long-term mental wellbeing] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Impact tests] - Based on the description you read, how well does this name work for the tab [Impact tests]</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t xml:space="preserve"> [Follow guidance to build my long-term mental wellbeing] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_17}].QSat</t>
+        </is>
+      </c>
       <c r="E129" t="b">
         <v>0</v>
       </c>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Q10_Combine. [Causal tests] - Based on the description you read, how well does this name work for the tab [Causal tests]</t>
+          <t>Qsat. [Get personalized recommendations on what to do next based on my data] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Q10_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Causal tests] - Based on the description you read, how well does this name work for the tab [Causal tests]</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t xml:space="preserve"> [Get personalized recommendations on what to do next based on my data] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_18}].QSat</t>
+        </is>
+      </c>
       <c r="E130" t="b">
         <v>0</v>
       </c>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Q11. [AB testing tab then Lift studies tab] - Which of the following names would you most prefer for this tab</t>
+          <t>Qsat. [Get motivation and accountability from friends and family] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [AB testing tab then Lift studies tab] - Which of the following names would you most prefer for this tab</t>
+          <t xml:space="preserve"> [Get motivation and accountability from friends and family] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_1}].Q11</t>
+          <t>Satisfaction_PrimaryApp_loop[{_19}].QSat</t>
         </is>
       </c>
       <c r="E131" t="b">
         <v>0</v>
       </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Q11. [Lift studies tab then AB testing tab] - Which of the following names would you most prefer for this tab</t>
+          <t>Qsat. [Share and celebrate my health achievements with others] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - Which of the following names would you most prefer for this tab</t>
+          <t xml:space="preserve"> [Share and celebrate my health achievements with others] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Q1Q12loop[{_2}].Q11</t>
+          <t>Satisfaction_PrimaryApp_loop[{_20}].QSat</t>
         </is>
       </c>
       <c r="E132" t="b">
         <v>0</v>
       </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Q11_Combine. [Lift studies tab then AB testing tab] - Which of the following names would you most prefer for this tab</t>
+          <t>Qsat. [Control who I'm connected with and what data I share] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Q11_Combine</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Lift studies tab then AB testing tab] - Which of the following names would you most prefer for this tab</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t xml:space="preserve"> [Control who I'm connected with and what data I share] - How satisfied are you with how Primary_app helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_21}].QSat</t>
+        </is>
+      </c>
       <c r="E133" t="b">
         <v>0</v>
       </c>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Q2. [Experiments] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t>Qsat. [Get answers to my health questions] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Qsat</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiments] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t xml:space="preserve"> [Get answers to my health questions] - How satisfied are you with how Primary_app helps you with this goal?</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Q2[{_1}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_22}].QSat</t>
         </is>
       </c>
       <c r="E134" t="b">
         <v>0</v>
       </c>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Qaware=yes</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Q2. [Tests] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t>Qfuture. [Review a quick summary of my daily health data at a glance] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Tests] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t xml:space="preserve"> [Review a quick summary of my daily health data at a glance] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Q2[{_2}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_1}].QFuture</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -3970,22 +4194,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Q2. [Experiment center] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t>Qfuture. [See my progress and trends over time] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiment center] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t xml:space="preserve"> [See my progress and trends over time] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Q2[{_3}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_2}].QFuture</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -3997,22 +4221,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Q2. [Testing hub] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t>Qfuture. [See all my health and wellness data from different apps in one place] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Testing hub] - Based on the following name, how interested are you in learning more about An area in Google Ads for comparing campaign versions?</t>
+          <t xml:space="preserve"> [See all my health and wellness data from different apps in one place] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Q2[{_4}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_3}].QFuture</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -4024,22 +4248,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Q3. [Helps me understand what the Google Ads product area] - We would now like to know more about what you think of when you see each name.</t>
+          <t>Qfuture. [Follow a structured workout or training plan] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Helps me understand what the Google Ads product area] - We would now like to know more about what you think of when you see each name</t>
+          <t xml:space="preserve"> [Follow a structured workout or training plan] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Q3[{_1}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_4}].QFuture</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -4051,22 +4275,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Q3. [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name.</t>
+          <t>Qfuture. [Accurately track a specific workout (e.g., a run, gym session)] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Uses clear, everyday language] - We would now like to know more about what you think of when you see each name</t>
+          <t xml:space="preserve"> [Accurately track a specific workout (eg, a run, gym session)] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Q3[{_2}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_5}].QFuture</t>
         </is>
       </c>
       <c r="E139" t="b">
@@ -4078,22 +4302,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Q3. [Leaves a positive impression] - We would now like to know more about what you think of when you see each name.</t>
+          <t>Qfuture. [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Leaves a positive impression] - We would now like to know more about what you think of when you see each name</t>
+          <t xml:space="preserve"> [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Q3[{_3}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_6}].QFuture</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -4105,22 +4329,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Q3. [Conveys innovative technology] - We would now like to know more about what you think of when you see each name.</t>
+          <t>Qfuture. [Understand my sleep quality, patterns, and duration] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Conveys innovative technology] - We would now like to know more about what you think of when you see each name</t>
+          <t xml:space="preserve"> [Understand my sleep quality, patterns, and duration] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Q3[{_4}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_7}].QFuture</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -4132,22 +4356,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Q3. [Sounds familiar] - We would now like to know more about what you think of when you see each name.</t>
+          <t>Qfuture. [Know if my body is physically recovered and ready for a workout] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Sounds familiar] - We would now like to know more about what you think of when you see each name</t>
+          <t xml:space="preserve"> [Know if my body is physically recovered and ready for a workout] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Q3[{_5}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_8}].QFuture</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -4159,22 +4383,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Q4. [Experiments] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t>Qfuture. [Build and maintain healthy sleep habits] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiments] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Build and maintain healthy sleep habits] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Q4[{_1}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_9}].QFuture</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -4186,22 +4410,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Q4. [Tests] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t>Qfuture. [Set health and fitness goals that are right for me] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Tests] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Set health and fitness goals that are right for me] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Q4[{_2}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_10}].QFuture</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -4213,22 +4437,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Q4. [Experiment center] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t>Qfuture. [Get recognized for my achievements (e.g., badges, awards)] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiment center] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Get recognized for my achievements (eg, badges, awards)] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Q4[{_3}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_11}].QFuture</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -4240,22 +4464,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Q4. [Testing hub] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t>Qfuture. [Track my nutrition and activity to reach a weight goal] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Testing hub] - Based on the description you read, how well does this name work for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Track my nutrition and activity to reach a weight goal] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Q4[{_4}]._scale</t>
+          <t>Satisfaction_PrimaryApp_loop[{_12}].QFuture</t>
         </is>
       </c>
       <c r="E146" t="b">
@@ -4267,20 +4491,24 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Q5. [Rank 1 - Summary] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t>Qfuture. [Accurately track my menstrual cycle and understand its patterns] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Rank 1 - Summary] - Which of the following names would you most prefer for this Google Ads product area?</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t xml:space="preserve"> [Accurately track my menstrual cycle and understand its patterns] - In the next 2-3 years, how important do you think this goal will be to you?</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_13}].QFuture</t>
+        </is>
+      </c>
       <c r="E147" t="b">
         <v>0</v>
       </c>
@@ -4290,20 +4518,24 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Q5. [Rank 1-2 - Summary] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t>Qfuture. [Easily log my mood, thoughts, or feelings] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Rank 1-2 - Summary] - Which of the following names would you most prefer for this Google Ads product area?</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t xml:space="preserve"> [Easily log my mood, thoughts, or feelings] - In the next 2-3 years, how important do you think this goal will be to you?</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_14}].QFuture</t>
+        </is>
+      </c>
       <c r="E148" t="b">
         <v>0</v>
       </c>
@@ -4313,20 +4545,24 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Q5. [Rank 1-3 - Summary] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t>Qfuture. [Track and manage my medication schedule] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Rank 1-3 - Summary] - Which of the following names would you most prefer for this Google Ads product area?</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t xml:space="preserve"> [Track and manage my medication schedule] - In the next 2-3 years, how important do you think this goal will be to you?</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Satisfaction_PrimaryApp_loop[{_15}].QFuture</t>
+        </is>
+      </c>
       <c r="E149" t="b">
         <v>0</v>
       </c>
@@ -4336,26 +4572,26 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Q5. [Experiments] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t>Qfuture. [Monitor key biomarkers like blood pressure or glucose] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiments] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Monitor key biomarkers like blood pressure or glucose] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Q5[{_1}]._scale_cat</t>
+          <t>Satisfaction_PrimaryApp_loop[{_16}].QFuture</t>
         </is>
       </c>
       <c r="E150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
@@ -4363,26 +4599,26 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Q5. [Tests] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t>Qfuture. [Follow guidance to build my long-term mental wellbeing] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Tests] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Follow guidance to build my long-term mental wellbeing] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Q5[{_2}]._scale_cat</t>
+          <t>Satisfaction_PrimaryApp_loop[{_17}].QFuture</t>
         </is>
       </c>
       <c r="E151" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
@@ -4390,26 +4626,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Q5. [Experiment center] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t>Qfuture. [Get personalized recommendations on what to do next based on my data] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Experiment center] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Get personalized recommendations on what to do next based on my data] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Q5[{_3}]._scale_cat</t>
+          <t>Satisfaction_PrimaryApp_loop[{_18}].QFuture</t>
         </is>
       </c>
       <c r="E152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
@@ -4417,26 +4653,26 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Q5. [Testing hub] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t>Qfuture. [Get motivation and accountability from friends and family] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Testing hub] - Which of the following names would you most prefer for this Google Ads product area?</t>
+          <t xml:space="preserve"> [Get motivation and accountability from friends and family] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Q5[{_4}]._scale_cat</t>
+          <t>Satisfaction_PrimaryApp_loop[{_19}].QFuture</t>
         </is>
       </c>
       <c r="E153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
@@ -4444,22 +4680,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Q_Placement. In the Google Ads UI, where would you expect to find a combined testing tool that include both experiments and lift studies?</t>
+          <t>Qfuture. [Share and celebrate my health achievements with others] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Q_Placement</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> In the Google Ads UI, where would you expect to find a combined testing tool that include both experiments and lift studies?</t>
+          <t xml:space="preserve"> [Share and celebrate my health achievements with others] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Q_Placement</t>
+          <t>Satisfaction_PrimaryApp_loop[{_20}].QFuture</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -4471,22 +4707,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Q_AB_and_Lift. Now, imagine you can measure the conversion lift of different variations of your campaigns. What would you call this?</t>
+          <t>Qfuture. [Control who I'm connected with and what data I share] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Q_AB_and_Lift</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Now, imagine you can measure the conversion lift of different variations of your campaigns What would you call this?</t>
+          <t xml:space="preserve"> [Control who I'm connected with and what data I share] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Q_AB_and_Lift</t>
+          <t>Satisfaction_PrimaryApp_loop[{_21}].QFuture</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -4498,22 +4734,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Q_certainty_of_winning. After you measure the lift of different variations of your campaigns, you get a report that shows the variation with the most lift and a percentage of how reliable the results are. Which of these names do you prefer for this percentage?</t>
+          <t>Qfuture. [Get answers to my health questions] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Q_certainty_of_winning</t>
+          <t>Qfuture</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> After you measure the lift of different variations of your campaigns, you get a report that shows the variation with the most lift and a percentage of how reliable the results are Which of these names do you prefer for this percentage?</t>
+          <t xml:space="preserve"> [Get answers to my health questions] - In the next 2-3 years, how important do you think this goal will be to you?</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Q_certainty_of_winning</t>
+          <t>Satisfaction_PrimaryApp_loop[{_22}].QFuture</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -4525,22 +4761,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Q_lift_metrics. A study that compares showing Campaign A vs not showing Campaign A produces a specific set of metrics. Which of these names do you prefer for those metrics?</t>
+          <t>Qsat2. - [Apple Health] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Q_lift_metrics</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A study that compares showing Campaign A vs not showing Campaign A produces a specific set of metrics Which of these names do you prefer for those metrics?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Q_lift_metrics</t>
+          <t>QSat2_loop[{_1}].QSat2[{_1}]._scale</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -4552,22 +4788,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Q_attribution_metrics. A study that compares Campaign A vs Campaign B produces a specific set of metrics. Which of these names do you prefer for those metrics?</t>
+          <t>Qsat2. - [Apple Health] - [See my progress and trends over time] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Q_attribution_metrics</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A study that compares Campaign A vs Campaign B produces a specific set of metrics Which of these names do you prefer for those metrics?</t>
+          <t xml:space="preserve"> - [Apple Health] - [See my progress and trends over time] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Q_attribution_metrics</t>
+          <t>QSat2_loop[{_1}].QSat2[{_2}]._scale</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -4579,22 +4815,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads A/B experiments operate in my best interest] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads A/B experiments operate in my best interest] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Qtrust[{_1}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_3}]._scale</t>
         </is>
       </c>
       <c r="E159" t="b">
@@ -4606,22 +4842,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads A/B experiments help me achieve high performing campaigns] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Follow a structured workout or training plan] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads A/B experiments help me achieve high performing campaigns] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Follow a structured workout or training plan] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Qtrust[{_2}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_4}]._scale</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -4633,22 +4869,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Qtrust. [The data from Google Ads A/B experiments is reliable] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Accurately track a specific workout (e.g., a run, gym session)] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [The data from Google Ads A/B experiments is reliable] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Accurately track a specific workout (eg, a run, gym session)] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Qtrust[{_3}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_5}]._scale</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -4660,22 +4896,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads A/B experiments provide helpful insights] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads A/B experiments provide helpful insights] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Qtrust[{_4}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_6}]._scale</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -4687,22 +4923,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Qtrust. [I can easily accomplish my tasks in Google Ads A/B experiment tools] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [I can easily accomplish my tasks in Google Ads A/B experiment tools] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Qtrust[{_5}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_7}]._scale</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -4714,22 +4950,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads Lift tests operate in my best interest] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads Lift tests operate in my best interest] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Qtrust[{_6}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_8}]._scale</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -4741,22 +4977,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads Lift tests help me achieve high performing campaigns] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Build and maintain healthy sleep habits] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads Lift tests help me achieve high performing campaigns] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Build and maintain healthy sleep habits] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Qtrust[{_7}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_9}]._scale</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -4768,22 +5004,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Qtrust. [The data from Google Ads Lift tests is reliable] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Set health and fitness goals that are right for me] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [The data from Google Ads Lift tests is reliable] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Set health and fitness goals that are right for me] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Qtrust[{_8}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_10}]._scale</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -4795,22 +5031,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads Lift tests provide helpful insights] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Get recognized for my achievements (e.g., badges, awards)] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads Lift tests provide helpful insights] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Get recognized for my achievements (eg, badges, awards)] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Qtrust[{_9}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_11}]._scale</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -4822,22 +5058,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Qtrust. [I can easily accomplish my tasks in Google Ads Lift tools] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [I can easily accomplish my tasks in Google Ads Lift tools] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Qtrust[{_10}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_12}]._scale</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -4849,22 +5085,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads Incrementality tests operate in my best interest] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads Incrementality tests operate in my best interest] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Qtrust[{_11}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_13}]._scale</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -4876,22 +5112,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads Incrementality tests help me achieve high performing campaigns] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads Incrementality tests help me achieve high performing campaigns] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Qtrust[{_12}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_14}]._scale</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -4903,22 +5139,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Qtrust. [The data from Google Ads Incrementality tests is reliable] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Track and manage my medication schedule] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [The data from Google Ads Incrementality tests is reliable] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Track and manage my medication schedule] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Qtrust[{_13}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_15}]._scale</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -4930,22 +5166,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Qtrust. [Google Ads Incrementality tests provide helpful insights] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [Google Ads Incrementality tests provide helpful insights] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Qtrust[{_14}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_16}]._scale</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -4957,22 +5193,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Qtrust. [I can easily accomplish my tasks in Google Ads Incrementality tools] - How much do you agree with each of the following statements?</t>
+          <t>Qsat2. - [Apple Health] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Qtrust</t>
+          <t>Qsat2</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [I can easily accomplish my tasks in Google Ads Incrementality tools] - How much do you agree with each of the following statements?</t>
+          <t xml:space="preserve"> - [Apple Health] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Qtrust[{_15}]._scale</t>
+          <t>QSat2_loop[{_1}].QSat2[{_17}]._scale</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -4980,6 +5216,3401 @@
       </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Apple Health] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Apple Health] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_1}].QSat2[{_18}]._scale</t>
+        </is>
+      </c>
+      <c r="E174" t="b">
+        <v>0</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Apple Health] - [Get motivation and accountability from friends and family] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Apple Health] - [Get motivation and accountability from friends and family] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_1}].QSat2[{_19}]._scale</t>
+        </is>
+      </c>
+      <c r="E175" t="b">
+        <v>0</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Apple Health] - [Share and celebrate my health achievements with others] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Apple Health] - [Share and celebrate my health achievements with others] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_1}].QSat2[{_20}]._scale</t>
+        </is>
+      </c>
+      <c r="E176" t="b">
+        <v>0</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Apple Health] - [Control who I'm connected with and what data I share] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Apple Health] - [Control who I'm connected with and what data I share] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_1}].QSat2[{_21}]._scale</t>
+        </is>
+      </c>
+      <c r="E177" t="b">
+        <v>0</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Apple Health] - [Get answers to my health questions] - You mentioned you also use [Apple Health]. How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Apple Health] - [Get answers to my health questions] - You mentioned you also use [Apple Health] How satisfied are you with how [Apple Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_1}].QSat2[{_22}]._scale</t>
+        </is>
+      </c>
+      <c r="E178" t="b">
+        <v>0</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_1}]._scale</t>
+        </is>
+      </c>
+      <c r="E179" t="b">
+        <v>0</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [See my progress and trends over time] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [See my progress and trends over time] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_2}]._scale</t>
+        </is>
+      </c>
+      <c r="E180" t="b">
+        <v>0</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_3}]._scale</t>
+        </is>
+      </c>
+      <c r="E181" t="b">
+        <v>0</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Follow a structured workout or training plan] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Follow a structured workout or training plan] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_4}]._scale</t>
+        </is>
+      </c>
+      <c r="E182" t="b">
+        <v>0</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Accurately track a specific workout (e.g., a run, gym session)] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Accurately track a specific workout (eg, a run, gym session)] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_5}]._scale</t>
+        </is>
+      </c>
+      <c r="E183" t="b">
+        <v>0</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_6}]._scale</t>
+        </is>
+      </c>
+      <c r="E184" t="b">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_7}]._scale</t>
+        </is>
+      </c>
+      <c r="E185" t="b">
+        <v>0</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_8}]._scale</t>
+        </is>
+      </c>
+      <c r="E186" t="b">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Build and maintain healthy sleep habits] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Build and maintain healthy sleep habits] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_9}]._scale</t>
+        </is>
+      </c>
+      <c r="E187" t="b">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Set health and fitness goals that are right for me] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Set health and fitness goals that are right for me] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_10}]._scale</t>
+        </is>
+      </c>
+      <c r="E188" t="b">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Get recognized for my achievements (e.g., badges, awards)] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Get recognized for my achievements (eg, badges, awards)] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_11}]._scale</t>
+        </is>
+      </c>
+      <c r="E189" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_12}]._scale</t>
+        </is>
+      </c>
+      <c r="E190" t="b">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_13}]._scale</t>
+        </is>
+      </c>
+      <c r="E191" t="b">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_14}]._scale</t>
+        </is>
+      </c>
+      <c r="E192" t="b">
+        <v>0</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Track and manage my medication schedule] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Track and manage my medication schedule] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_15}]._scale</t>
+        </is>
+      </c>
+      <c r="E193" t="b">
+        <v>0</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_16}]._scale</t>
+        </is>
+      </c>
+      <c r="E194" t="b">
+        <v>0</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_17}]._scale</t>
+        </is>
+      </c>
+      <c r="E195" t="b">
+        <v>0</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_18}]._scale</t>
+        </is>
+      </c>
+      <c r="E196" t="b">
+        <v>0</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Get motivation and accountability from friends and family] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Get motivation and accountability from friends and family] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_19}]._scale</t>
+        </is>
+      </c>
+      <c r="E197" t="b">
+        <v>0</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Share and celebrate my health achievements with others] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Share and celebrate my health achievements with others] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_20}]._scale</t>
+        </is>
+      </c>
+      <c r="E198" t="b">
+        <v>0</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Control who I'm connected with and what data I share] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Control who I'm connected with and what data I share] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_21}]._scale</t>
+        </is>
+      </c>
+      <c r="E199" t="b">
+        <v>0</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Fitbit / Fitbit Premium] - [Get answers to my health questions] - You mentioned you also use [Fitbit / Fitbit Premium]. How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Fitbit / Fitbit Premium] - [Get answers to my health questions] - You mentioned you also use [Fitbit / Fitbit Premium] How satisfied are you with how [Fitbit / Fitbit Premium] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_2}].QSat2[{_22}]._scale</t>
+        </is>
+      </c>
+      <c r="E200" t="b">
+        <v>0</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_1}]._scale</t>
+        </is>
+      </c>
+      <c r="E201" t="b">
+        <v>0</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [See my progress and trends over time] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [See my progress and trends over time] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_2}]._scale</t>
+        </is>
+      </c>
+      <c r="E202" t="b">
+        <v>0</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_3}]._scale</t>
+        </is>
+      </c>
+      <c r="E203" t="b">
+        <v>0</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Follow a structured workout or training plan] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Follow a structured workout or training plan] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_4}]._scale</t>
+        </is>
+      </c>
+      <c r="E204" t="b">
+        <v>0</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Accurately track a specific workout (e.g., a run, gym session)] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Accurately track a specific workout (eg, a run, gym session)] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_5}]._scale</t>
+        </is>
+      </c>
+      <c r="E205" t="b">
+        <v>0</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_6}]._scale</t>
+        </is>
+      </c>
+      <c r="E206" t="b">
+        <v>0</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_7}]._scale</t>
+        </is>
+      </c>
+      <c r="E207" t="b">
+        <v>0</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_8}]._scale</t>
+        </is>
+      </c>
+      <c r="E208" t="b">
+        <v>0</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Build and maintain healthy sleep habits] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Build and maintain healthy sleep habits] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_9}]._scale</t>
+        </is>
+      </c>
+      <c r="E209" t="b">
+        <v>0</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Set health and fitness goals that are right for me] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Set health and fitness goals that are right for me] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_10}]._scale</t>
+        </is>
+      </c>
+      <c r="E210" t="b">
+        <v>0</v>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Get recognized for my achievements (e.g., badges, awards)] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Get recognized for my achievements (eg, badges, awards)] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_11}]._scale</t>
+        </is>
+      </c>
+      <c r="E211" t="b">
+        <v>0</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_12}]._scale</t>
+        </is>
+      </c>
+      <c r="E212" t="b">
+        <v>0</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_13}]._scale</t>
+        </is>
+      </c>
+      <c r="E213" t="b">
+        <v>0</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_14}]._scale</t>
+        </is>
+      </c>
+      <c r="E214" t="b">
+        <v>0</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Track and manage my medication schedule] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Track and manage my medication schedule] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_15}]._scale</t>
+        </is>
+      </c>
+      <c r="E215" t="b">
+        <v>0</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_16}]._scale</t>
+        </is>
+      </c>
+      <c r="E216" t="b">
+        <v>0</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_17}]._scale</t>
+        </is>
+      </c>
+      <c r="E217" t="b">
+        <v>0</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_18}]._scale</t>
+        </is>
+      </c>
+      <c r="E218" t="b">
+        <v>0</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Get motivation and accountability from friends and family] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Get motivation and accountability from friends and family] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_19}]._scale</t>
+        </is>
+      </c>
+      <c r="E219" t="b">
+        <v>0</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Share and celebrate my health achievements with others] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Share and celebrate my health achievements with others] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_20}]._scale</t>
+        </is>
+      </c>
+      <c r="E220" t="b">
+        <v>0</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Control who I'm connected with and what data I share] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Control who I'm connected with and what data I share] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_21}]._scale</t>
+        </is>
+      </c>
+      <c r="E221" t="b">
+        <v>0</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Garmin Connect] - [Get answers to my health questions] - You mentioned you also use [Garmin Connect]. How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Garmin Connect] - [Get answers to my health questions] - You mentioned you also use [Garmin Connect] How satisfied are you with how [Garmin Connect] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_3}].QSat2[{_22}]._scale</t>
+        </is>
+      </c>
+      <c r="E222" t="b">
+        <v>0</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_1}]._scale</t>
+        </is>
+      </c>
+      <c r="E223" t="b">
+        <v>0</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [See my progress and trends over time] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [See my progress and trends over time] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_2}]._scale</t>
+        </is>
+      </c>
+      <c r="E224" t="b">
+        <v>0</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_3}]._scale</t>
+        </is>
+      </c>
+      <c r="E225" t="b">
+        <v>0</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Follow a structured workout or training plan] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Follow a structured workout or training plan] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_4}]._scale</t>
+        </is>
+      </c>
+      <c r="E226" t="b">
+        <v>0</v>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Accurately track a specific workout (e.g., a run, gym session)] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Accurately track a specific workout (eg, a run, gym session)] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_5}]._scale</t>
+        </is>
+      </c>
+      <c r="E227" t="b">
+        <v>0</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_6}]._scale</t>
+        </is>
+      </c>
+      <c r="E228" t="b">
+        <v>0</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_7}]._scale</t>
+        </is>
+      </c>
+      <c r="E229" t="b">
+        <v>0</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_8}]._scale</t>
+        </is>
+      </c>
+      <c r="E230" t="b">
+        <v>0</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Build and maintain healthy sleep habits] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Build and maintain healthy sleep habits] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_9}]._scale</t>
+        </is>
+      </c>
+      <c r="E231" t="b">
+        <v>0</v>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Set health and fitness goals that are right for me] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Set health and fitness goals that are right for me] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_10}]._scale</t>
+        </is>
+      </c>
+      <c r="E232" t="b">
+        <v>0</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Get recognized for my achievements (e.g., badges, awards)] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Get recognized for my achievements (eg, badges, awards)] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_11}]._scale</t>
+        </is>
+      </c>
+      <c r="E233" t="b">
+        <v>0</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_12}]._scale</t>
+        </is>
+      </c>
+      <c r="E234" t="b">
+        <v>0</v>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_13}]._scale</t>
+        </is>
+      </c>
+      <c r="E235" t="b">
+        <v>0</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_14}]._scale</t>
+        </is>
+      </c>
+      <c r="E236" t="b">
+        <v>0</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Track and manage my medication schedule] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Track and manage my medication schedule] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_15}]._scale</t>
+        </is>
+      </c>
+      <c r="E237" t="b">
+        <v>0</v>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_16}]._scale</t>
+        </is>
+      </c>
+      <c r="E238" t="b">
+        <v>0</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_17}]._scale</t>
+        </is>
+      </c>
+      <c r="E239" t="b">
+        <v>0</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_18}]._scale</t>
+        </is>
+      </c>
+      <c r="E240" t="b">
+        <v>0</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Get motivation and accountability from friends and family] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Get motivation and accountability from friends and family] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_19}]._scale</t>
+        </is>
+      </c>
+      <c r="E241" t="b">
+        <v>0</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Share and celebrate my health achievements with others] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Share and celebrate my health achievements with others] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_20}]._scale</t>
+        </is>
+      </c>
+      <c r="E242" t="b">
+        <v>0</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Control who I'm connected with and what data I share] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Control who I'm connected with and what data I share] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_21}]._scale</t>
+        </is>
+      </c>
+      <c r="E243" t="b">
+        <v>0</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Oura App] - [Get answers to my health questions] - You mentioned you also use [Oura App]. How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Oura App] - [Get answers to my health questions] - You mentioned you also use [Oura App] How satisfied are you with how [Oura App] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_4}].QSat2[{_22}]._scale</t>
+        </is>
+      </c>
+      <c r="E244" t="b">
+        <v>0</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_1}]._scale</t>
+        </is>
+      </c>
+      <c r="E245" t="b">
+        <v>0</v>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [See my progress and trends over time] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [See my progress and trends over time] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_2}]._scale</t>
+        </is>
+      </c>
+      <c r="E246" t="b">
+        <v>0</v>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_3}]._scale</t>
+        </is>
+      </c>
+      <c r="E247" t="b">
+        <v>0</v>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Follow a structured workout or training plan] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Follow a structured workout or training plan] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_4}]._scale</t>
+        </is>
+      </c>
+      <c r="E248" t="b">
+        <v>0</v>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Accurately track a specific workout (e.g., a run, gym session)] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Accurately track a specific workout (eg, a run, gym session)] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_5}]._scale</t>
+        </is>
+      </c>
+      <c r="E249" t="b">
+        <v>0</v>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_6}]._scale</t>
+        </is>
+      </c>
+      <c r="E250" t="b">
+        <v>0</v>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_7}]._scale</t>
+        </is>
+      </c>
+      <c r="E251" t="b">
+        <v>0</v>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_8}]._scale</t>
+        </is>
+      </c>
+      <c r="E252" t="b">
+        <v>0</v>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Build and maintain healthy sleep habits] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Build and maintain healthy sleep habits] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_9}]._scale</t>
+        </is>
+      </c>
+      <c r="E253" t="b">
+        <v>0</v>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Set health and fitness goals that are right for me] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Set health and fitness goals that are right for me] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_10}]._scale</t>
+        </is>
+      </c>
+      <c r="E254" t="b">
+        <v>0</v>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Get recognized for my achievements (e.g., badges, awards)] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Get recognized for my achievements (eg, badges, awards)] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_11}]._scale</t>
+        </is>
+      </c>
+      <c r="E255" t="b">
+        <v>0</v>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_12}]._scale</t>
+        </is>
+      </c>
+      <c r="E256" t="b">
+        <v>0</v>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_13}]._scale</t>
+        </is>
+      </c>
+      <c r="E257" t="b">
+        <v>0</v>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_14}]._scale</t>
+        </is>
+      </c>
+      <c r="E258" t="b">
+        <v>0</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Track and manage my medication schedule] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Track and manage my medication schedule] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_15}]._scale</t>
+        </is>
+      </c>
+      <c r="E259" t="b">
+        <v>0</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_16}]._scale</t>
+        </is>
+      </c>
+      <c r="E260" t="b">
+        <v>0</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_17}]._scale</t>
+        </is>
+      </c>
+      <c r="E261" t="b">
+        <v>0</v>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_18}]._scale</t>
+        </is>
+      </c>
+      <c r="E262" t="b">
+        <v>0</v>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Get motivation and accountability from friends and family] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Get motivation and accountability from friends and family] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_19}]._scale</t>
+        </is>
+      </c>
+      <c r="E263" t="b">
+        <v>0</v>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Share and celebrate my health achievements with others] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Share and celebrate my health achievements with others] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_20}]._scale</t>
+        </is>
+      </c>
+      <c r="E264" t="b">
+        <v>0</v>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Control who I'm connected with and what data I share] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Control who I'm connected with and what data I share] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_21}]._scale</t>
+        </is>
+      </c>
+      <c r="E265" t="b">
+        <v>0</v>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Samsung Health] - [Get answers to my health questions] - You mentioned you also use [Samsung Health]. How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Samsung Health] - [Get answers to my health questions] - You mentioned you also use [Samsung Health] How satisfied are you with how [Samsung Health] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_5}].QSat2[{_22}]._scale</t>
+        </is>
+      </c>
+      <c r="E266" t="b">
+        <v>0</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Review a quick summary of my daily health data at a glance] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_1}]._scale</t>
+        </is>
+      </c>
+      <c r="E267" t="b">
+        <v>0</v>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [See my progress and trends over time] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [See my progress and trends over time] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_2}]._scale</t>
+        </is>
+      </c>
+      <c r="E268" t="b">
+        <v>0</v>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [See all my health and wellness data from different apps in one place] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_3}]._scale</t>
+        </is>
+      </c>
+      <c r="E269" t="b">
+        <v>0</v>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Follow a structured workout or training plan] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Follow a structured workout or training plan] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_4}]._scale</t>
+        </is>
+      </c>
+      <c r="E270" t="b">
+        <v>0</v>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Accurately track a specific workout (e.g., a run, gym session)] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Accurately track a specific workout (eg, a run, gym session)] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_5}]._scale</t>
+        </is>
+      </c>
+      <c r="E271" t="b">
+        <v>0</v>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Get real-time feedback during my workouts (e.g., pace, heart rate zones)] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Get real-time feedback during my workouts (eg, pace, heart rate zones)] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_6}]._scale</t>
+        </is>
+      </c>
+      <c r="E272" t="b">
+        <v>0</v>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Understand my sleep quality, patterns, and duration] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_7}]._scale</t>
+        </is>
+      </c>
+      <c r="E273" t="b">
+        <v>0</v>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Know if my body is physically recovered and ready for a workout] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_8}]._scale</t>
+        </is>
+      </c>
+      <c r="E274" t="b">
+        <v>0</v>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Build and maintain healthy sleep habits] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Build and maintain healthy sleep habits] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_9}]._scale</t>
+        </is>
+      </c>
+      <c r="E275" t="b">
+        <v>0</v>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Set health and fitness goals that are right for me] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Set health and fitness goals that are right for me] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_10}]._scale</t>
+        </is>
+      </c>
+      <c r="E276" t="b">
+        <v>0</v>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Get recognized for my achievements (e.g., badges, awards)] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Get recognized for my achievements (eg, badges, awards)] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_11}]._scale</t>
+        </is>
+      </c>
+      <c r="E277" t="b">
+        <v>0</v>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Track my nutrition and activity to reach a weight goal] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_12}]._scale</t>
+        </is>
+      </c>
+      <c r="E278" t="b">
+        <v>0</v>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Accurately track my menstrual cycle and understand its patterns] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_13}]._scale</t>
+        </is>
+      </c>
+      <c r="E279" t="b">
+        <v>0</v>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Easily log my mood, thoughts, or feelings] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_14}]._scale</t>
+        </is>
+      </c>
+      <c r="E280" t="b">
+        <v>0</v>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Track and manage my medication schedule] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Track and manage my medication schedule] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_15}]._scale</t>
+        </is>
+      </c>
+      <c r="E281" t="b">
+        <v>0</v>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Monitor key biomarkers like blood pressure or glucose] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_16}]._scale</t>
+        </is>
+      </c>
+      <c r="E282" t="b">
+        <v>0</v>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Follow guidance to build my long-term mental wellbeing] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_17}]._scale</t>
+        </is>
+      </c>
+      <c r="E283" t="b">
+        <v>0</v>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Get personalized recommendations on what to do next based on my data] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_18}]._scale</t>
+        </is>
+      </c>
+      <c r="E284" t="b">
+        <v>0</v>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Get motivation and accountability from friends and family] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Get motivation and accountability from friends and family] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_19}]._scale</t>
+        </is>
+      </c>
+      <c r="E285" t="b">
+        <v>0</v>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Share and celebrate my health achievements with others] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Share and celebrate my health achievements with others] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_20}]._scale</t>
+        </is>
+      </c>
+      <c r="E286" t="b">
+        <v>0</v>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Control who I'm connected with and what data I share] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Control who I'm connected with and what data I share] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_21}]._scale</t>
+        </is>
+      </c>
+      <c r="E287" t="b">
+        <v>0</v>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Qsat2. - [Strava] - [Get answers to my health questions] - You mentioned you also use [Strava]. How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Qsat2</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - [Strava] - [Get answers to my health questions] - You mentioned you also use [Strava] How satisfied are you with how [Strava] helps you with this goal?</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>QSat2_loop[{_6}].QSat2[{_22}]._scale</t>
+        </is>
+      </c>
+      <c r="E288" t="b">
+        <v>0</v>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Qsat_ecosystem. Overall, how satisfied are you with how your total system of apps/devices helps you achieve your health goals?</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Qsat_ecosystem</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Overall, how satisfied are you with how your total system of apps/devices helps you achieve your health goals?</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>QSat_ecosystem</t>
+        </is>
+      </c>
+      <c r="E289" t="b">
+        <v>0</v>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Single_vs_ecosystem_marker=Micro-Ecosystem users</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>TT1. What are your current health goals?</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>TT1</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> What are your current health goals?</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>TT1</t>
+        </is>
+      </c>
+      <c r="E290" t="b">
+        <v>0</v>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>TT1_P. Which of the goals you selected previously is most important to you right now?</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>TT1_P</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Which of the goals you selected previously is most important to you right now?</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>TT1_P</t>
+        </is>
+      </c>
+      <c r="E291" t="b">
+        <v>0</v>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>EX1. Which of the following types of exercise do you perform regularly, if any?</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>EX1</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Which of the following types of exercise do you perform regularly, if any?</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>EX1</t>
+        </is>
+      </c>
+      <c r="E292" t="b">
+        <v>0</v>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>EX2. [Running / Jogging (indoor or outdoor)] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>EX2</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [Running / Jogging (indoor or outdoor)] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>EX2[{_1}]._scale</t>
+        </is>
+      </c>
+      <c r="E293" t="b">
+        <v>0</v>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>EX1 = 1,3,8,11</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>EX2. [Strength training (Weight lifting or Body weight exercises)] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>EX2</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [Strength training (Weight lifting or Body weight exercises)] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>EX2[{_2}]._scale</t>
+        </is>
+      </c>
+      <c r="E294" t="b">
+        <v>0</v>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>EX1 = 1,3,8,11</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>EX2. [Cycling (outdoor)] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>EX2</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [Cycling (outdoor)] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>EX2[{_3}]._scale</t>
+        </is>
+      </c>
+      <c r="E295" t="b">
+        <v>0</v>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>EX1 = 1,3,8,11</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>EX2. [Swimming] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>EX2</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [Swimming] - How would you describe your level of experience with the types of exercise you perform regularly?</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>EX2[{_4}]._scale</t>
+        </is>
+      </c>
+      <c r="E296" t="b">
+        <v>0</v>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>EX1 = 1,3,8,11</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Profile_marker. Profile_marker</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Profile_marker</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Profile_marker</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Profile_marker</t>
+        </is>
+      </c>
+      <c r="E297" t="b">
+        <v>0</v>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>QCountry. Select the country you want to test.</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>QCountry</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Select the country you want to test</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>QCountry</t>
+        </is>
+      </c>
+      <c r="E298" t="b">
+        <v>0</v>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
